--- a/Models/Овцы и козы/results/Овцы и козы - Результаты прогнозов SARIMA средние.xlsx
+++ b/Models/Овцы и козы/results/Овцы и козы - Результаты прогнозов SARIMA средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.6</v>
+        <v>83.69</v>
       </c>
       <c r="C2" t="n">
-        <v>48.21</v>
+        <v>77.2</v>
       </c>
       <c r="D2" t="n">
-        <v>6.86</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>158.3</v>
+        <v>128.68</v>
       </c>
       <c r="C3" t="n">
-        <v>139.45</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>8.289999999999999</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>385.19</v>
+        <v>352.25</v>
       </c>
       <c r="C4" t="n">
-        <v>301.24</v>
+        <v>266.76</v>
       </c>
       <c r="D4" t="n">
-        <v>13.86</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.87</v>
+        <v>122.68</v>
       </c>
       <c r="C5" t="n">
-        <v>67.18000000000001</v>
+        <v>95.38</v>
       </c>
       <c r="D5" t="n">
-        <v>7.21</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>181.82</v>
+        <v>114.58</v>
       </c>
       <c r="C6" t="n">
-        <v>161.02</v>
+        <v>93.14</v>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4</v>
+        <v>1.16</v>
       </c>
       <c r="C7" t="n">
-        <v>0.29</v>
+        <v>0.84</v>
       </c>
       <c r="D7" t="n">
-        <v>1.938945707226866e+21</v>
+        <v>2.903022200075226e+21</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="C8" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="D8" t="n">
-        <v>9.390000000000001</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39.13</v>
+        <v>30.49</v>
       </c>
       <c r="C9" t="n">
-        <v>27.03</v>
+        <v>24.08</v>
       </c>
       <c r="D9" t="n">
-        <v>24.68</v>
+        <v>26.15</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>172.88</v>
+        <v>125.31</v>
       </c>
       <c r="C10" t="n">
-        <v>152.05</v>
+        <v>107.3</v>
       </c>
       <c r="D10" t="n">
-        <v>5.76</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>64.84999999999999</v>
+        <v>60.57</v>
       </c>
       <c r="C11" t="n">
-        <v>59.28</v>
+        <v>52.6</v>
       </c>
       <c r="D11" t="n">
-        <v>3.97</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>86.61</v>
+        <v>56.12</v>
       </c>
       <c r="C12" t="n">
-        <v>75.23</v>
+        <v>49.55</v>
       </c>
       <c r="D12" t="n">
-        <v>8.52</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42.93</v>
+        <v>39.16</v>
       </c>
       <c r="C13" t="n">
-        <v>37.23</v>
+        <v>34.35</v>
       </c>
       <c r="D13" t="n">
-        <v>18.93</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>84.79000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="C14" t="n">
-        <v>68.66</v>
+        <v>72.73</v>
       </c>
       <c r="D14" t="n">
-        <v>14.49</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.92</v>
+        <v>16.25</v>
       </c>
       <c r="C15" t="n">
-        <v>9.33</v>
+        <v>14.5</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>534.45</v>
+        <v>208.58</v>
       </c>
       <c r="C16" t="n">
-        <v>406.14</v>
+        <v>179.71</v>
       </c>
       <c r="D16" t="n">
-        <v>30.5</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>681.04</v>
+        <v>161.81</v>
       </c>
       <c r="C17" t="n">
-        <v>661.25</v>
+        <v>118.59</v>
       </c>
       <c r="D17" t="n">
-        <v>63.65</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>151.46</v>
+        <v>31.04</v>
       </c>
       <c r="C18" t="n">
-        <v>135.46</v>
+        <v>20.9</v>
       </c>
       <c r="D18" t="n">
-        <v>31.37</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>56.32</v>
+        <v>59.79</v>
       </c>
       <c r="C19" t="n">
-        <v>47.46</v>
+        <v>50.74</v>
       </c>
       <c r="D19" t="n">
-        <v>6.04</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30.87</v>
+        <v>22.33</v>
       </c>
       <c r="C20" t="n">
-        <v>28.87</v>
+        <v>21.24</v>
       </c>
       <c r="D20" t="n">
-        <v>8.279999999999999</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>724.67</v>
+        <v>803.4</v>
       </c>
       <c r="C21" t="n">
-        <v>639.38</v>
+        <v>658.48</v>
       </c>
       <c r="D21" t="n">
-        <v>14.9</v>
+        <v>12.21</v>
       </c>
     </row>
   </sheetData>
